--- a/output/graficos_regionales/plot_regional_serie_i_ingr_mean_m_2023_maule.xlsx
+++ b/output/graficos_regionales/plot_regional_serie_i_ingr_mean_m_2023_maule.xlsx
@@ -288,7 +288,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-28 16:44</t>
+    <t xml:space="preserve">2026-10-05 02:05</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -704,7 +704,7 @@
         <v>223244.75</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>307926.12</v>
+        <v>307926.13</v>
       </c>
     </row>
     <row r="3">
@@ -847,7 +847,7 @@
         <v>231217.72</v>
       </c>
       <c r="C15" s="2" t="n">
-        <v>324105.12</v>
+        <v>324105.13</v>
       </c>
     </row>
     <row r="16">
@@ -913,7 +913,7 @@
         <v>232307.89</v>
       </c>
       <c r="C21" s="2" t="n">
-        <v>329863.62</v>
+        <v>329863.63</v>
       </c>
     </row>
     <row r="22">
@@ -1064,7 +1064,7 @@
         <v>36</v>
       </c>
       <c r="B35" s="2" t="n">
-        <v>235830.12</v>
+        <v>235830.13</v>
       </c>
       <c r="C35" s="2" t="n">
         <v>321537.41</v>
@@ -1075,7 +1075,7 @@
         <v>37</v>
       </c>
       <c r="B36" s="2" t="n">
-        <v>253434.12</v>
+        <v>253434.13</v>
       </c>
       <c r="C36" s="2" t="n">
         <v>334145.66</v>
@@ -1287,7 +1287,7 @@
         <v>280671.28</v>
       </c>
       <c r="C55" s="2" t="n">
-        <v>391178.62</v>
+        <v>391178.63</v>
       </c>
     </row>
     <row r="56">
@@ -1529,7 +1529,7 @@
         <v>321614.25</v>
       </c>
       <c r="C77" s="2" t="n">
-        <v>440497.12</v>
+        <v>440497.13</v>
       </c>
     </row>
     <row r="78">
@@ -1592,10 +1592,10 @@
         <v>84</v>
       </c>
       <c r="B83" s="2" t="n">
-        <v>326607.12</v>
+        <v>326607.13</v>
       </c>
       <c r="C83" s="2" t="n">
-        <v>451935.62</v>
+        <v>451935.63</v>
       </c>
     </row>
     <row r="84">
